--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/CREACION DE CARPETAS/resultado_prueba_carpetas.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/CREACION DE CARPETAS/resultado_prueba_carpetas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F373"/>
+  <dimension ref="A1:F372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,16 +489,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0035-2024</t>
+          <t>0200-2023</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -508,23 +508,23 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0035-2024</t>
+          <t>INFORME 04 ABRIL 2026 0200-2023</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0051-2025</t>
+          <t>0215-2024</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -534,23 +534,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0051-2025</t>
+          <t>INFORME 04 ABRIL 2026 0215-2024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0051-2023</t>
+          <t>0216-2024</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -560,23 +560,23 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0051-2023</t>
+          <t>INFORME 04 ABRIL 2026 0216-2024</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0087-2023</t>
+          <t>0222-2025</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -586,23 +586,23 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0087-2023</t>
+          <t>INFORME 04 ABRIL 2026 0222-2025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0102-2024</t>
+          <t>0245-2024</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -612,23 +612,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0102-2024</t>
+          <t>INFORME 04 ABRIL 2026 0245-2024</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0106-2023</t>
+          <t>0249-2024</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -638,23 +638,23 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0106-2023</t>
+          <t>INFORME 04 ABRIL 2026 0249-2024</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0112-2023</t>
+          <t>0256-2019</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -664,23 +664,23 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0112-2023</t>
+          <t>INFORME 04 ABRIL 2026 0256-2019</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0116-2024</t>
+          <t>0263-2022</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -690,49 +690,49 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0116-2024</t>
+          <t>INFORME 04 ABRIL 2026 0263-2022</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0116-2026</t>
+          <t>0264-2022</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>2026</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>INFORME 02 MARZO 2026 0116-2026</t>
+          <t>INFORME 04 ABRIL 2026 0264-2022</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0171-2026</t>
+          <t>0265-2022</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -742,23 +742,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0171-2026</t>
+          <t>INFORME 04 ABRIL 2026 0265-2022</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0185-2025</t>
+          <t>0272-2024</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -768,23 +768,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0185-2025</t>
+          <t>INFORME 04 ABRIL 2026 0272-2024</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0189-2019</t>
+          <t>0276-2022</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -794,23 +794,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0189-2019</t>
+          <t>INFORME 04 ABRIL 2026 0276-2022</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0190-2022</t>
+          <t>0280-2022</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -820,23 +820,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0190-2022</t>
+          <t>INFORME 04 ABRIL 2026 0280-2022</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0192-2025</t>
+          <t>0289-2024</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -846,23 +846,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0192-2025</t>
+          <t>INFORME 04 ABRIL 2026 0289-2024</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0196-2025</t>
+          <t>0292-2022</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -872,23 +872,23 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0196-2025</t>
+          <t>INFORME 04 ABRIL 2026 0292-2022</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0215-2024</t>
+          <t>0296-2022</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -898,23 +898,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0215-2024</t>
+          <t>INFORME 04 ABRIL 2026 0296-2022</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0216-2024</t>
+          <t>0304-2022</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -924,23 +924,23 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0216-2024</t>
+          <t>INFORME 04 ABRIL 2026 0304-2022</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0222-2025</t>
+          <t>0318-2024</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -950,23 +950,23 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0222-2025</t>
+          <t>INFORME 04 ABRIL 2026 0318-2024</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0245-2024</t>
+          <t>0331-2023</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -976,23 +976,23 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0245-2024</t>
+          <t>INFORME 04 ABRIL 2026 0331-2023</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0249-2024</t>
+          <t>0334-2025</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1002,23 +1002,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0249-2024</t>
+          <t>INFORME 04 ABRIL 2026 0334-2025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0263-2022</t>
+          <t>0350-2022</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -1028,23 +1028,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0263-2022</t>
+          <t>INFORME 04 ABRIL 2026 0350-2022</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0264-2022</t>
+          <t>0352-2025</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -1054,23 +1054,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0264-2022</t>
+          <t>INFORME 04 ABRIL 2026 0352-2025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0265-2022</t>
+          <t>0372-2022</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0265-2022</t>
+          <t>INFORME 04 ABRIL 2026 0372-2022</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0272-2024</t>
+          <t>0380-2025</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0272-2024</t>
+          <t>INFORME 04 ABRIL 2026 0380-2025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0276-2022</t>
+          <t>0380-2026</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1132,23 +1132,23 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0276-2022</t>
+          <t>INFORME 04 ABRIL 2026 0380-2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0280-2022</t>
+          <t>0381-2022</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -1158,23 +1158,23 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0280-2022</t>
+          <t>INFORME 04 ABRIL 2026 0381-2022</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0289-2024</t>
+          <t>0381-2026</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -1184,23 +1184,23 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0289-2024</t>
+          <t>INFORME 04 ABRIL 2026 0381-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0292-2022</t>
+          <t>0411-2021</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -1210,23 +1210,23 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0292-2022</t>
+          <t>INFORME 04 ABRIL 2026 0411-2021</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0296-2022</t>
+          <t>0411-2024</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -1236,23 +1236,23 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0296-2022</t>
+          <t>INFORME 04 ABRIL 2026 0411-2024</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0318-2024</t>
+          <t>0468-2022</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -1262,23 +1262,23 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0318-2024</t>
+          <t>INFORME 04 ABRIL 2026 0468-2022</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0334-2025</t>
+          <t>0474-2024</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
@@ -1288,23 +1288,23 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0334-2025</t>
+          <t>INFORME 04 ABRIL 2026 0474-2024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0352-2025</t>
+          <t>0488-2023</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -1314,23 +1314,23 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0352-2025</t>
+          <t>INFORME 04 ABRIL 2026 0488-2023</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0380-2025</t>
+          <t>0490-2023</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
@@ -1340,49 +1340,49 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0380-2025</t>
+          <t>INFORME 04 ABRIL 2026 0490-2023</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0380-2026</t>
+          <t>0515-2024</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>2026</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>INFORME 02 MARZO 2026 0380-2026</t>
+          <t>INFORME 04 ABRIL 2026 0515-2024</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0381-2022</t>
+          <t>0566-2025</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -1392,49 +1392,49 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0381-2022</t>
+          <t>INFORME 04 ABRIL 2026 0566-2025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0381-2026</t>
+          <t>0618-2025</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>2026</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>INFORME 02 MARZO 2026 0381-2026</t>
+          <t>INFORME 04 ABRIL 2026 0618-2025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0411-2021</t>
+          <t>0626-2019</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
@@ -1444,23 +1444,23 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0411-2021</t>
+          <t>INFORME 04 ABRIL 2026 0626-2019</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0411-2024</t>
+          <t>0660-2025</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
@@ -1470,23 +1470,23 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0411-2024</t>
+          <t>INFORME 04 ABRIL 2026 0660-2025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0468-2022</t>
+          <t>0700-2024</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
@@ -1496,23 +1496,23 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0468-2022</t>
+          <t>INFORME 04 ABRIL 2026 0700-2024</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Andrés Suárez Gutiérrez</t>
+          <t>Ana Maria Pinzon Medina</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0474-2024</t>
+          <t>0984-2021</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0474-2024</t>
+          <t>INFORME 04 ABRIL 2026 0984-2021</t>
         </is>
       </c>
     </row>
@@ -1534,11 +1534,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0488-2023</t>
+          <t>0189-2019</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0488-2023</t>
+          <t>INFORME 04 ABRIL 2026 0189-2019</t>
         </is>
       </c>
     </row>
@@ -1560,11 +1560,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0490-2023</t>
+          <t>0190-2022</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0490-2023</t>
+          <t>INFORME 04 ABRIL 2026 0190-2022</t>
         </is>
       </c>
     </row>
@@ -1586,11 +1586,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0513-2025</t>
+          <t>0192-2025</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0513-2025</t>
+          <t>INFORME 04 ABRIL 2026 0192-2025</t>
         </is>
       </c>
     </row>
@@ -1612,11 +1612,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0530-2025</t>
+          <t>0196-2025</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0530-2025</t>
+          <t>INFORME 04 ABRIL 2026 0196-2025</t>
         </is>
       </c>
     </row>
@@ -1638,11 +1638,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0534-2024</t>
+          <t>0513-2025</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0534-2024</t>
+          <t>INFORME 04 ABRIL 2026 0513-2025</t>
         </is>
       </c>
     </row>
@@ -1664,11 +1664,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0545-2025</t>
+          <t>0530-2025</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0545-2025</t>
+          <t>INFORME 04 ABRIL 2026 0530-2025</t>
         </is>
       </c>
     </row>
@@ -1690,11 +1690,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0546-2023</t>
+          <t>0534-2024</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0546-2023</t>
+          <t>INFORME 04 ABRIL 2026 0534-2024</t>
         </is>
       </c>
     </row>
@@ -1716,11 +1716,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0559-2024</t>
+          <t>0545-2025</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0559-2024</t>
+          <t>INFORME 04 ABRIL 2026 0545-2025</t>
         </is>
       </c>
     </row>
@@ -1742,11 +1742,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0572-2023</t>
+          <t>0546-2023</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0572-2023</t>
+          <t>INFORME 04 ABRIL 2026 0546-2023</t>
         </is>
       </c>
     </row>
@@ -1768,11 +1768,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0593-2024</t>
+          <t>0559-2024</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0593-2024</t>
+          <t>INFORME 04 ABRIL 2026 0559-2024</t>
         </is>
       </c>
     </row>
@@ -1794,11 +1794,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0606-2025</t>
+          <t>0572-2023</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0606-2025</t>
+          <t>INFORME 04 ABRIL 2026 0572-2023</t>
         </is>
       </c>
     </row>
@@ -1820,11 +1820,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0642-2021</t>
+          <t>0593-2024</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0642-2021</t>
+          <t>INFORME 04 ABRIL 2026 0593-2024</t>
         </is>
       </c>
     </row>
@@ -1846,11 +1846,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0653-2023</t>
+          <t>0606-2025</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0653-2023</t>
+          <t>INFORME 04 ABRIL 2026 0606-2025</t>
         </is>
       </c>
     </row>
@@ -1872,11 +1872,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0654-2024</t>
+          <t>0642-2021</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0654-2024</t>
+          <t>INFORME 04 ABRIL 2026 0642-2021</t>
         </is>
       </c>
     </row>
@@ -1898,11 +1898,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0662-2024</t>
+          <t>0653-2023</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0662-2024</t>
+          <t>INFORME 04 ABRIL 2026 0653-2023</t>
         </is>
       </c>
     </row>
@@ -1924,11 +1924,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0690-2025</t>
+          <t>0654-2024</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0690-2025</t>
+          <t>INFORME 04 ABRIL 2026 0654-2024</t>
         </is>
       </c>
     </row>
@@ -1950,11 +1950,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0702-2023</t>
+          <t>0662-2024</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0702-2023</t>
+          <t>INFORME 04 ABRIL 2026 0662-2024</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0706-2024</t>
+          <t>0690-2025</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0706-2024</t>
+          <t>INFORME 04 ABRIL 2026 0690-2025</t>
         </is>
       </c>
     </row>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0732-2024</t>
+          <t>0702-2023</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0732-2024</t>
+          <t>INFORME 04 ABRIL 2026 0702-2023</t>
         </is>
       </c>
     </row>
@@ -2028,11 +2028,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0734-2024</t>
+          <t>0706-2024</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0734-2024</t>
+          <t>INFORME 04 ABRIL 2026 0706-2024</t>
         </is>
       </c>
     </row>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0737-2024</t>
+          <t>0732-2024</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0737-2024</t>
+          <t>INFORME 04 ABRIL 2026 0732-2024</t>
         </is>
       </c>
     </row>
@@ -2080,11 +2080,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0739-2024</t>
+          <t>0734-2024</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0739-2024</t>
+          <t>INFORME 04 ABRIL 2026 0734-2024</t>
         </is>
       </c>
     </row>
@@ -2106,11 +2106,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0748-2024</t>
+          <t>0737-2024</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0748-2024</t>
+          <t>INFORME 04 ABRIL 2026 0737-2024</t>
         </is>
       </c>
     </row>
@@ -2132,11 +2132,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0758-2021</t>
+          <t>0739-2024</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0758-2021</t>
+          <t>INFORME 04 ABRIL 2026 0739-2024</t>
         </is>
       </c>
     </row>
@@ -2158,11 +2158,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0758-2024</t>
+          <t>0748-2024</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0758-2024</t>
+          <t>INFORME 04 ABRIL 2026 0748-2024</t>
         </is>
       </c>
     </row>
@@ -2184,11 +2184,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0764-2021</t>
+          <t>0758-2024</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0764-2021</t>
+          <t>INFORME 04 ABRIL 2026 0758-2024</t>
         </is>
       </c>
     </row>
@@ -2210,11 +2210,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0769-2024</t>
+          <t>0764-2021</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0769-2024</t>
+          <t>INFORME 04 ABRIL 2026 0764-2021</t>
         </is>
       </c>
     </row>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0779-2024</t>
+          <t>0769-2024</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0779-2024</t>
+          <t>INFORME 04 ABRIL 2026 0769-2024</t>
         </is>
       </c>
     </row>
@@ -2262,11 +2262,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0786-2024</t>
+          <t>0779-2024</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0786-2024</t>
+          <t>INFORME 04 ABRIL 2026 0779-2024</t>
         </is>
       </c>
     </row>
@@ -2288,11 +2288,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0789-2021</t>
+          <t>0786-2024</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0789-2021</t>
+          <t>INFORME 04 ABRIL 2026 0786-2024</t>
         </is>
       </c>
     </row>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0796-2025</t>
+          <t>0789-2021</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0796-2025</t>
+          <t>INFORME 04 ABRIL 2026 0789-2021</t>
         </is>
       </c>
     </row>
@@ -2340,11 +2340,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0807-2025</t>
+          <t>0796-2025</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0807-2025</t>
+          <t>INFORME 04 ABRIL 2026 0796-2025</t>
         </is>
       </c>
     </row>
@@ -2366,11 +2366,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0815-2025</t>
+          <t>0807-2025</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0815-2025</t>
+          <t>INFORME 04 ABRIL 2026 0807-2025</t>
         </is>
       </c>
     </row>
@@ -2392,11 +2392,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0818-2025</t>
+          <t>0815-2025</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0818-2025</t>
+          <t>INFORME 04 ABRIL 2026 0815-2025</t>
         </is>
       </c>
     </row>
@@ -2418,11 +2418,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0827-2021</t>
+          <t>0818-2025</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0827-2021</t>
+          <t>INFORME 04 ABRIL 2026 0818-2025</t>
         </is>
       </c>
     </row>
@@ -2444,11 +2444,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0829-2024</t>
+          <t>0827-2021</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0829-2024</t>
+          <t>INFORME 04 ABRIL 2026 0827-2021</t>
         </is>
       </c>
     </row>
@@ -2470,11 +2470,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0850-2025</t>
+          <t>0829-2024</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0850-2025</t>
+          <t>INFORME 04 ABRIL 2026 0829-2024</t>
         </is>
       </c>
     </row>
@@ -2496,11 +2496,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0855-2025</t>
+          <t>0850-2025</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0855-2025</t>
+          <t>INFORME 04 ABRIL 2026 0850-2025</t>
         </is>
       </c>
     </row>
@@ -2522,11 +2522,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0856-2024</t>
+          <t>0855-2025</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0856-2024</t>
+          <t>INFORME 04 ABRIL 2026 0855-2025</t>
         </is>
       </c>
     </row>
@@ -2548,11 +2548,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0859-2021</t>
+          <t>0856-2024</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0859-2021</t>
+          <t>INFORME 04 ABRIL 2026 0856-2024</t>
         </is>
       </c>
     </row>
@@ -2574,11 +2574,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0862-2024</t>
+          <t>0859-2021</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0862-2024</t>
+          <t>INFORME 04 ABRIL 2026 0859-2021</t>
         </is>
       </c>
     </row>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0865-2024</t>
+          <t>0862-2024</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
         <v>1</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0865-2024</t>
+          <t>INFORME 04 ABRIL 2026 0862-2024</t>
         </is>
       </c>
     </row>
@@ -2626,11 +2626,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0872-2024</t>
+          <t>0865-2024</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0872-2024</t>
+          <t>INFORME 04 ABRIL 2026 0865-2024</t>
         </is>
       </c>
     </row>
@@ -2652,11 +2652,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0875-2025</t>
+          <t>0872-2024</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0875-2025</t>
+          <t>INFORME 04 ABRIL 2026 0872-2024</t>
         </is>
       </c>
     </row>
@@ -2678,11 +2678,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0884-2025</t>
+          <t>0875-2025</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0884-2025</t>
+          <t>INFORME 04 ABRIL 2026 0875-2025</t>
         </is>
       </c>
     </row>
@@ -2704,11 +2704,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0890-2024</t>
+          <t>0884-2025</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0890-2024</t>
+          <t>INFORME 04 ABRIL 2026 0884-2025</t>
         </is>
       </c>
     </row>
@@ -2730,11 +2730,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0905-2024</t>
+          <t>0890-2024</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0905-2024</t>
+          <t>INFORME 04 ABRIL 2026 0890-2024</t>
         </is>
       </c>
     </row>
@@ -2756,11 +2756,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0910-2024</t>
+          <t>0905-2024</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0910-2024</t>
+          <t>INFORME 04 ABRIL 2026 0905-2024</t>
         </is>
       </c>
     </row>
@@ -2782,11 +2782,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0936-2024</t>
+          <t>0910-2024</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
@@ -2796,23 +2796,23 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0936-2024</t>
+          <t>INFORME 04 ABRIL 2026 0910-2024</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Eldrin Jose Orozco</t>
+          <t>Andrés Suárez Gutiérrez</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0009-2025</t>
+          <t>0936-2024</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0009-2025</t>
+          <t>INFORME 04 ABRIL 2026 0936-2024</t>
         </is>
       </c>
     </row>
@@ -2834,11 +2834,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0037-2025</t>
+          <t>0009-2025</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0037-2025</t>
+          <t>INFORME 04 ABRIL 2026 0009-2025</t>
         </is>
       </c>
     </row>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0040-2025</t>
+          <t>0037-2025</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0040-2025</t>
+          <t>INFORME 04 ABRIL 2026 0037-2025</t>
         </is>
       </c>
     </row>
@@ -2886,11 +2886,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0049-2024</t>
+          <t>0040-2025</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0049-2024</t>
+          <t>INFORME 04 ABRIL 2026 0040-2025</t>
         </is>
       </c>
     </row>
@@ -2912,11 +2912,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0069-2020</t>
+          <t>0049-2024</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0069-2020</t>
+          <t>INFORME 04 ABRIL 2026 0049-2024</t>
         </is>
       </c>
     </row>
@@ -2938,11 +2938,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0074-2024</t>
+          <t>0069-2020</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0074-2024</t>
+          <t>INFORME 04 ABRIL 2026 0069-2020</t>
         </is>
       </c>
     </row>
@@ -2964,11 +2964,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0091-2026</t>
+          <t>0074-2024</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0091-2026</t>
+          <t>INFORME 04 ABRIL 2026 0074-2024</t>
         </is>
       </c>
     </row>
@@ -2990,11 +2990,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0124-2026</t>
+          <t>0091-2026</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0124-2026</t>
+          <t>INFORME 04 ABRIL 2026 0091-2026</t>
         </is>
       </c>
     </row>
@@ -3016,11 +3016,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0269-2024</t>
+          <t>0124-2026</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
         <v>1</v>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0269-2024</t>
+          <t>INFORME 04 ABRIL 2026 0124-2026</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0269-2022</t>
+          <t>INFORME 04 ABRIL 2026 0269-2022</t>
         </is>
       </c>
     </row>
@@ -3068,11 +3068,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0272-2022</t>
+          <t>0269-2024</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0272-2022</t>
+          <t>INFORME 04 ABRIL 2026 0269-2024</t>
         </is>
       </c>
     </row>
@@ -3094,11 +3094,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0273-2022</t>
+          <t>0272-2022</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0273-2022</t>
+          <t>INFORME 04 ABRIL 2026 0272-2022</t>
         </is>
       </c>
     </row>
@@ -3120,11 +3120,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0283-2021</t>
+          <t>0273-2022</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0283-2021</t>
+          <t>INFORME 04 ABRIL 2026 0273-2022</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0286-2022</t>
+          <t>INFORME 04 ABRIL 2026 0286-2022</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0289-2022</t>
+          <t>INFORME 04 ABRIL 2026 0289-2022</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0291-2022</t>
+          <t>INFORME 04 ABRIL 2026 0291-2022</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0293-2024</t>
+          <t>INFORME 04 ABRIL 2026 0293-2024</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0295-2022</t>
+          <t>INFORME 04 ABRIL 2026 0295-2022</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0296-2024</t>
+          <t>INFORME 04 ABRIL 2026 0296-2024</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0297-2025</t>
+          <t>INFORME 04 ABRIL 2026 0297-2025</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0299-2022</t>
+          <t>INFORME 04 ABRIL 2026 0299-2022</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0299-2025</t>
+          <t>INFORME 04 ABRIL 2026 0299-2025</t>
         </is>
       </c>
     </row>
@@ -3380,11 +3380,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0307-2023</t>
+          <t>0307-2022</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0307-2023</t>
+          <t>INFORME 04 ABRIL 2026 0307-2022</t>
         </is>
       </c>
     </row>
@@ -3406,11 +3406,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0307-2022</t>
+          <t>0307-2023</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0307-2022</t>
+          <t>INFORME 04 ABRIL 2026 0307-2023</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0309-2022</t>
+          <t>INFORME 04 ABRIL 2026 0309-2022</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0317-2021</t>
+          <t>INFORME 04 ABRIL 2026 0317-2021</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
         <v>1</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0318-2021</t>
+          <t>INFORME 04 ABRIL 2026 0318-2021</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0320-2023</t>
+          <t>INFORME 04 ABRIL 2026 0320-2023</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0343-2022</t>
+          <t>INFORME 04 ABRIL 2026 0343-2022</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0368-2022</t>
+          <t>INFORME 04 ABRIL 2026 0368-2022</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0371-2024</t>
+          <t>INFORME 04 ABRIL 2026 0371-2024</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0379-2025</t>
+          <t>INFORME 04 ABRIL 2026 0379-2025</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0382-2022</t>
+          <t>INFORME 04 ABRIL 2026 0382-2022</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0388-2025</t>
+          <t>INFORME 04 ABRIL 2026 0388-2025</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
         <v>1</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0404-2025</t>
+          <t>INFORME 04 ABRIL 2026 0404-2025</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D127" t="n">
         <v>1</v>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0459-2025</t>
+          <t>INFORME 04 ABRIL 2026 0459-2025</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0474-2022</t>
+          <t>INFORME 04 ABRIL 2026 0474-2022</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0497-2022</t>
+          <t>INFORME 04 ABRIL 2026 0497-2022</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0514-2024</t>
+          <t>INFORME 04 ABRIL 2026 0514-2024</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0539-2021</t>
+          <t>INFORME 04 ABRIL 2026 0539-2021</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D132" t="n">
         <v>1</v>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0540-2025</t>
+          <t>INFORME 04 ABRIL 2026 0540-2025</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0561-2024</t>
+          <t>INFORME 04 ABRIL 2026 0561-2024</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D134" t="n">
         <v>1</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0564-2021</t>
+          <t>INFORME 04 ABRIL 2026 0564-2021</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0565-2021</t>
+          <t>INFORME 04 ABRIL 2026 0565-2021</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D136" t="n">
         <v>1</v>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0579-2021</t>
+          <t>INFORME 04 ABRIL 2026 0579-2021</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>1</v>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0608-2024</t>
+          <t>INFORME 04 ABRIL 2026 0608-2024</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0611-2025</t>
+          <t>INFORME 04 ABRIL 2026 0611-2025</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
         <v>1</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0621-2024</t>
+          <t>INFORME 04 ABRIL 2026 0621-2024</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0625-2023</t>
+          <t>INFORME 04 ABRIL 2026 0625-2023</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0639-2024</t>
+          <t>INFORME 04 ABRIL 2026 0639-2024</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0646-2024</t>
+          <t>INFORME 04 ABRIL 2026 0646-2024</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D143" t="n">
         <v>1</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0656-2024</t>
+          <t>INFORME 04 ABRIL 2026 0656-2024</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D144" t="n">
         <v>1</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0663-2024</t>
+          <t>INFORME 04 ABRIL 2026 0663-2024</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0666-2020</t>
+          <t>INFORME 04 ABRIL 2026 0666-2020</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D146" t="n">
         <v>1</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0697-2024</t>
+          <t>INFORME 04 ABRIL 2026 0697-2024</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D147" t="n">
         <v>1</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0710-2024</t>
+          <t>INFORME 04 ABRIL 2026 0710-2024</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D148" t="n">
         <v>1</v>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0712-2023</t>
+          <t>INFORME 04 ABRIL 2026 0712-2023</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D149" t="n">
         <v>1</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0713-2024</t>
+          <t>INFORME 04 ABRIL 2026 0713-2024</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D150" t="n">
         <v>1</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0714-2024</t>
+          <t>INFORME 04 ABRIL 2026 0714-2024</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D151" t="n">
         <v>1</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0718-2024</t>
+          <t>INFORME 04 ABRIL 2026 0718-2024</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D152" t="n">
         <v>1</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0721-2024</t>
+          <t>INFORME 04 ABRIL 2026 0721-2024</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D153" t="n">
         <v>1</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0725-2024</t>
+          <t>INFORME 04 ABRIL 2026 0725-2024</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D154" t="n">
         <v>1</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0727-2024</t>
+          <t>INFORME 04 ABRIL 2026 0727-2024</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0728-2024</t>
+          <t>INFORME 04 ABRIL 2026 0728-2024</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D156" t="n">
         <v>1</v>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0729-2023</t>
+          <t>INFORME 04 ABRIL 2026 0729-2023</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
         <v>1</v>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0733-2024</t>
+          <t>INFORME 04 ABRIL 2026 0733-2024</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
         <v>1</v>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0738-2024</t>
+          <t>INFORME 04 ABRIL 2026 0738-2024</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D159" t="n">
         <v>1</v>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0739-2021</t>
+          <t>INFORME 04 ABRIL 2026 0739-2021</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D160" t="n">
         <v>1</v>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0741-2024</t>
+          <t>INFORME 04 ABRIL 2026 0741-2024</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
         <v>1</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0752-2025</t>
+          <t>INFORME 04 ABRIL 2026 0752-2025</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
         <v>1</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0757-2025</t>
+          <t>INFORME 04 ABRIL 2026 0757-2025</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0761-2023</t>
+          <t>INFORME 04 ABRIL 2026 0761-2023</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
         <v>1</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0763-2023</t>
+          <t>INFORME 04 ABRIL 2026 0763-2023</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
         <v>1</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0765-2025</t>
+          <t>INFORME 04 ABRIL 2026 0765-2025</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
         <v>1</v>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0773-2023</t>
+          <t>INFORME 04 ABRIL 2026 0773-2023</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0778-2025</t>
+          <t>INFORME 04 ABRIL 2026 0778-2025</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
         <v>1</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0789-2024</t>
+          <t>INFORME 04 ABRIL 2026 0789-2024</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D169" t="n">
         <v>1</v>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0792-2025</t>
+          <t>INFORME 04 ABRIL 2026 0792-2025</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0794-2025</t>
+          <t>INFORME 04 ABRIL 2026 0794-2025</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0801-2025</t>
+          <t>INFORME 04 ABRIL 2026 0801-2025</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D172" t="n">
         <v>1</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0805-2025</t>
+          <t>INFORME 04 ABRIL 2026 0805-2025</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0808-2025</t>
+          <t>INFORME 04 ABRIL 2026 0808-2025</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D174" t="n">
         <v>1</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0820-2025</t>
+          <t>INFORME 04 ABRIL 2026 0820-2025</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D175" t="n">
         <v>1</v>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0859-2024</t>
+          <t>INFORME 04 ABRIL 2026 0859-2024</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D176" t="n">
         <v>1</v>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0861-2025</t>
+          <t>INFORME 04 ABRIL 2026 0861-2025</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D177" t="n">
         <v>1</v>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0862-2025</t>
+          <t>INFORME 04 ABRIL 2026 0862-2025</t>
         </is>
       </c>
     </row>
@@ -5044,11 +5044,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0869-2025</t>
+          <t>0869-2021</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D178" t="n">
         <v>1</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0869-2025</t>
+          <t>INFORME 04 ABRIL 2026 0869-2021</t>
         </is>
       </c>
     </row>
@@ -5070,11 +5070,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0869-2021</t>
+          <t>0869-2025</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D179" t="n">
         <v>1</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0869-2021</t>
+          <t>INFORME 04 ABRIL 2026 0869-2025</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
         <v>1</v>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0881-2024</t>
+          <t>INFORME 04 ABRIL 2026 0881-2024</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D181" t="n">
         <v>1</v>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0888-2024</t>
+          <t>INFORME 04 ABRIL 2026 0888-2024</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D182" t="n">
         <v>1</v>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0903-2021</t>
+          <t>INFORME 04 ABRIL 2026 0903-2021</t>
         </is>
       </c>
     </row>
@@ -5174,11 +5174,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0904-2024</t>
+          <t>0904-2021</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D183" t="n">
         <v>1</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0904-2024</t>
+          <t>INFORME 04 ABRIL 2026 0904-2021</t>
         </is>
       </c>
     </row>
@@ -5200,11 +5200,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0904-2021</t>
+          <t>0904-2024</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0904-2021</t>
+          <t>INFORME 04 ABRIL 2026 0904-2024</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
         <v>1</v>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0905-2021</t>
+          <t>INFORME 04 ABRIL 2026 0905-2021</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D186" t="n">
         <v>1</v>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0916-2021</t>
+          <t>INFORME 04 ABRIL 2026 0916-2021</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D187" t="n">
         <v>1</v>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0920-2024</t>
+          <t>INFORME 04 ABRIL 2026 0920-2024</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D188" t="n">
         <v>1</v>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0933-2021</t>
+          <t>INFORME 04 ABRIL 2026 0933-2021</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D189" t="n">
         <v>1</v>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0939-2024</t>
+          <t>INFORME 04 ABRIL 2026 0939-2024</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D190" t="n">
         <v>1</v>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0941-2024</t>
+          <t>INFORME 04 ABRIL 2026 0941-2024</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D191" t="n">
         <v>1</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0954-2024</t>
+          <t>INFORME 04 ABRIL 2026 0954-2024</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D192" t="n">
         <v>1</v>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0004-2021</t>
+          <t>INFORME 04 ABRIL 2026 0004-2021</t>
         </is>
       </c>
     </row>
@@ -5434,11 +5434,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0004-2022</t>
+          <t>0050-2024</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D193" t="n">
         <v>1</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0004-2022</t>
+          <t>INFORME 04 ABRIL 2026 0050-2024</t>
         </is>
       </c>
     </row>
@@ -5460,11 +5460,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0050-2024</t>
+          <t>0092-2026</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D194" t="n">
         <v>1</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0050-2024</t>
+          <t>INFORME 04 ABRIL 2026 0092-2026</t>
         </is>
       </c>
     </row>
@@ -5486,21 +5486,21 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0092-2026</t>
+          <t>0125-2026</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" t="n">
         <v>2026</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>INFORME 02 MARZO 2026 0092-2026</t>
+          <t>INFORME 04 ABRIL 2026 0125-2026</t>
         </is>
       </c>
     </row>
@@ -5512,21 +5512,21 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0125-2026</t>
+          <t>0259-2022</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
         <v>2026</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>INFORME 02 MARZO 2026 0125-2026</t>
+          <t>INFORME 04 ABRIL 2026 0259-2022</t>
         </is>
       </c>
     </row>
@@ -5538,11 +5538,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0138-2025</t>
+          <t>0296-2025</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D197" t="n">
         <v>1</v>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0138-2025</t>
+          <t>INFORME 04 ABRIL 2026 0296-2025</t>
         </is>
       </c>
     </row>
@@ -5564,11 +5564,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0200-2023</t>
+          <t>0301-2023</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D198" t="n">
         <v>1</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0200-2023</t>
+          <t>INFORME 04 ABRIL 2026 0301-2023</t>
         </is>
       </c>
     </row>
@@ -5590,11 +5590,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0231-2024</t>
+          <t>0350-2025</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D199" t="n">
         <v>1</v>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0231-2024</t>
+          <t>INFORME 04 ABRIL 2026 0350-2025</t>
         </is>
       </c>
     </row>
@@ -5616,11 +5616,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0256-2019</t>
+          <t>0355-2025</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D200" t="n">
         <v>1</v>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0256-2019</t>
+          <t>INFORME 04 ABRIL 2026 0355-2025</t>
         </is>
       </c>
     </row>
@@ -5642,11 +5642,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0259-2022</t>
+          <t>0393-2023</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D201" t="n">
         <v>1</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0259-2022</t>
+          <t>INFORME 04 ABRIL 2026 0393-2023</t>
         </is>
       </c>
     </row>
@@ -5668,11 +5668,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0278-2020</t>
+          <t>0407-2022</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D202" t="n">
         <v>1</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0278-2020</t>
+          <t>INFORME 04 ABRIL 2026 0407-2022</t>
         </is>
       </c>
     </row>
@@ -5694,11 +5694,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0284-2022</t>
+          <t>0409-2020</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D203" t="n">
         <v>1</v>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0284-2022</t>
+          <t>INFORME 04 ABRIL 2026 0409-2020</t>
         </is>
       </c>
     </row>
@@ -5720,11 +5720,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0296-2025</t>
+          <t>0433-2025</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D204" t="n">
         <v>1</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0296-2025</t>
+          <t>INFORME 04 ABRIL 2026 0433-2025</t>
         </is>
       </c>
     </row>
@@ -5746,11 +5746,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0300-2022</t>
+          <t>0462-2023</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D205" t="n">
         <v>1</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0300-2022</t>
+          <t>INFORME 04 ABRIL 2026 0462-2023</t>
         </is>
       </c>
     </row>
@@ -5772,11 +5772,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0301-2023</t>
+          <t>0475-2024</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D206" t="n">
         <v>1</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0301-2023</t>
+          <t>INFORME 04 ABRIL 2026 0475-2024</t>
         </is>
       </c>
     </row>
@@ -5798,11 +5798,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0350-2025</t>
+          <t>0484-2023</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0350-2025</t>
+          <t>INFORME 04 ABRIL 2026 0484-2023</t>
         </is>
       </c>
     </row>
@@ -5824,11 +5824,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0355-2025</t>
+          <t>0488-2025</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D208" t="n">
         <v>1</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0355-2025</t>
+          <t>INFORME 04 ABRIL 2026 0488-2025</t>
         </is>
       </c>
     </row>
@@ -5850,11 +5850,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0393-2023</t>
+          <t>0492-2026</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D209" t="n">
         <v>1</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0393-2023</t>
+          <t>INFORME 04 ABRIL 2026 0492-2026</t>
         </is>
       </c>
     </row>
@@ -5876,11 +5876,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0407-2022</t>
+          <t>0493-2025</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D210" t="n">
         <v>1</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0407-2022</t>
+          <t>INFORME 04 ABRIL 2026 0493-2025</t>
         </is>
       </c>
     </row>
@@ -5902,11 +5902,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0409-2020</t>
+          <t>0501-2024</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D211" t="n">
         <v>1</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0409-2020</t>
+          <t>INFORME 04 ABRIL 2026 0501-2024</t>
         </is>
       </c>
     </row>
@@ -5928,11 +5928,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>0433-2025</t>
+          <t>0539-2025</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D212" t="n">
         <v>1</v>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0433-2025</t>
+          <t>INFORME 04 ABRIL 2026 0539-2025</t>
         </is>
       </c>
     </row>
@@ -5954,11 +5954,11 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>0462-2023</t>
+          <t>0542-2024</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D213" t="n">
         <v>1</v>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0462-2023</t>
+          <t>INFORME 04 ABRIL 2026 0542-2024</t>
         </is>
       </c>
     </row>
@@ -5980,11 +5980,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>0475-2024</t>
+          <t>0560-2024</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D214" t="n">
         <v>1</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0475-2024</t>
+          <t>INFORME 04 ABRIL 2026 0560-2024</t>
         </is>
       </c>
     </row>
@@ -6006,11 +6006,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>0484-2023</t>
+          <t>0562-2020</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D215" t="n">
         <v>1</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0484-2023</t>
+          <t>INFORME 04 ABRIL 2026 0562-2020</t>
         </is>
       </c>
     </row>
@@ -6032,11 +6032,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0488-2025</t>
+          <t>0578-2025</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D216" t="n">
         <v>1</v>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0488-2025</t>
+          <t>INFORME 04 ABRIL 2026 0578-2025</t>
         </is>
       </c>
     </row>
@@ -6058,21 +6058,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0492-2026</t>
+          <t>0582-2024</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E217" t="n">
         <v>2026</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>INFORME 02 MARZO 2026 0492-2026</t>
+          <t>INFORME 04 ABRIL 2026 0582-2024</t>
         </is>
       </c>
     </row>
@@ -6084,11 +6084,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0493-2025</t>
+          <t>0594-2023</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D218" t="n">
         <v>1</v>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0493-2025</t>
+          <t>INFORME 04 ABRIL 2026 0594-2023</t>
         </is>
       </c>
     </row>
@@ -6110,11 +6110,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0501-2024</t>
+          <t>0594-2024</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D219" t="n">
         <v>1</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0501-2024</t>
+          <t>INFORME 04 ABRIL 2026 0594-2024</t>
         </is>
       </c>
     </row>
@@ -6136,11 +6136,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>0513-2023</t>
+          <t>0596-2024</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D220" t="n">
         <v>1</v>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0513-2023</t>
+          <t>INFORME 04 ABRIL 2026 0596-2024</t>
         </is>
       </c>
     </row>
@@ -6162,11 +6162,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0518-2025</t>
+          <t>0610-2025</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D221" t="n">
         <v>1</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0518-2025</t>
+          <t>INFORME 04 ABRIL 2026 0610-2025</t>
         </is>
       </c>
     </row>
@@ -6188,11 +6188,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0527-2025</t>
+          <t>0611-2024</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D222" t="n">
         <v>1</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0527-2025</t>
+          <t>INFORME 04 ABRIL 2026 0611-2024</t>
         </is>
       </c>
     </row>
@@ -6214,11 +6214,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0539-2025</t>
+          <t>0613-2023</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D223" t="n">
         <v>1</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0539-2025</t>
+          <t>INFORME 04 ABRIL 2026 0613-2023</t>
         </is>
       </c>
     </row>
@@ -6240,11 +6240,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0542-2024</t>
+          <t>0643-2024</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D224" t="n">
         <v>1</v>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0542-2024</t>
+          <t>INFORME 04 ABRIL 2026 0643-2024</t>
         </is>
       </c>
     </row>
@@ -6266,11 +6266,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0560-2024</t>
+          <t>0661-2020</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D225" t="n">
         <v>1</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0560-2024</t>
+          <t>INFORME 04 ABRIL 2026 0661-2020</t>
         </is>
       </c>
     </row>
@@ -6292,11 +6292,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>0562-2020</t>
+          <t>0687-2025</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D226" t="n">
         <v>1</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0562-2020</t>
+          <t>INFORME 04 ABRIL 2026 0687-2025</t>
         </is>
       </c>
     </row>
@@ -6318,11 +6318,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0567-2023</t>
+          <t>0749-2024</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D227" t="n">
         <v>1</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0567-2023</t>
+          <t>INFORME 04 ABRIL 2026 0749-2024</t>
         </is>
       </c>
     </row>
@@ -6344,11 +6344,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0578-2025</t>
+          <t>0758-2021</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D228" t="n">
         <v>1</v>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0578-2025</t>
+          <t>INFORME 04 ABRIL 2026 0758-2021</t>
         </is>
       </c>
     </row>
@@ -6370,11 +6370,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0582-2024</t>
+          <t>0795-2024</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D229" t="n">
         <v>1</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0582-2024</t>
+          <t>INFORME 04 ABRIL 2026 0795-2024</t>
         </is>
       </c>
     </row>
@@ -6396,11 +6396,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0594-2023</t>
+          <t>0816-2025</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D230" t="n">
         <v>1</v>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0594-2023</t>
+          <t>INFORME 04 ABRIL 2026 0816-2025</t>
         </is>
       </c>
     </row>
@@ -6422,11 +6422,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0594-2024</t>
+          <t>0827-2025</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D231" t="n">
         <v>1</v>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0594-2024</t>
+          <t>INFORME 04 ABRIL 2026 0827-2025</t>
         </is>
       </c>
     </row>
@@ -6448,11 +6448,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0596-2024</t>
+          <t>0835-2025</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D232" t="n">
         <v>1</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0596-2024</t>
+          <t>INFORME 04 ABRIL 2026 0835-2025</t>
         </is>
       </c>
     </row>
@@ -6474,11 +6474,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0610-2025</t>
+          <t>0837-2024</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D233" t="n">
         <v>1</v>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0610-2025</t>
+          <t>INFORME 04 ABRIL 2026 0837-2024</t>
         </is>
       </c>
     </row>
@@ -6500,11 +6500,11 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0611-2024</t>
+          <t>0877-2025</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D234" t="n">
         <v>1</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0611-2024</t>
+          <t>INFORME 04 ABRIL 2026 0877-2025</t>
         </is>
       </c>
     </row>
@@ -6526,11 +6526,11 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>0613-2023</t>
+          <t>0890-2025</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D235" t="n">
         <v>1</v>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0613-2023</t>
+          <t>INFORME 04 ABRIL 2026 0890-2025</t>
         </is>
       </c>
     </row>
@@ -6552,11 +6552,11 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0626-2019</t>
+          <t>0911-2021</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D236" t="n">
         <v>1</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0626-2019</t>
+          <t>INFORME 04 ABRIL 2026 0911-2021</t>
         </is>
       </c>
     </row>
@@ -6578,11 +6578,11 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>0632-2023</t>
+          <t>0911-2025</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D237" t="n">
         <v>1</v>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0632-2023</t>
+          <t>INFORME 04 ABRIL 2026 0911-2025</t>
         </is>
       </c>
     </row>
@@ -6604,11 +6604,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>0649-2023</t>
+          <t>0935-2024</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D238" t="n">
         <v>1</v>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0649-2023</t>
+          <t>INFORME 04 ABRIL 2026 0935-2024</t>
         </is>
       </c>
     </row>
@@ -6630,11 +6630,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>0661-2020</t>
+          <t>0937-2024</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D239" t="n">
         <v>1</v>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0661-2020</t>
+          <t>INFORME 04 ABRIL 2026 0937-2024</t>
         </is>
       </c>
     </row>
@@ -6656,11 +6656,11 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>0687-2025</t>
+          <t>0948-2021</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D240" t="n">
         <v>1</v>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0687-2025</t>
+          <t>INFORME 04 ABRIL 2026 0948-2021</t>
         </is>
       </c>
     </row>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>0688-2023</t>
+          <t>0952-2024</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D241" t="n">
         <v>1</v>
@@ -6696,23 +6696,23 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0688-2023</t>
+          <t>INFORME 04 ABRIL 2026 0952-2024</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>0723-2024</t>
+          <t>0304-2025</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D242" t="n">
         <v>1</v>
@@ -6722,23 +6722,23 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0723-2024</t>
+          <t>INFORME 04 ABRIL 2026 0304-2025</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0726-2024</t>
+          <t>0325-2023</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D243" t="n">
         <v>1</v>
@@ -6748,23 +6748,23 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0726-2024</t>
+          <t>INFORME 04 ABRIL 2026 0325-2023</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0749-2024</t>
+          <t>0370-2023</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D244" t="n">
         <v>1</v>
@@ -6774,23 +6774,23 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0749-2024</t>
+          <t>INFORME 04 ABRIL 2026 0370-2023</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>0751-2025</t>
+          <t>0405-2024</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D245" t="n">
         <v>1</v>
@@ -6800,23 +6800,23 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0751-2025</t>
+          <t>INFORME 04 ABRIL 2026 0405-2024</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>0753-2025</t>
+          <t>0458-2025</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D246" t="n">
         <v>1</v>
@@ -6826,23 +6826,23 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0753-2025</t>
+          <t>INFORME 04 ABRIL 2026 0458-2025</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>0759-2025</t>
+          <t>0464-2022</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D247" t="n">
         <v>1</v>
@@ -6852,23 +6852,23 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0759-2025</t>
+          <t>INFORME 04 ABRIL 2026 0464-2022</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>0791-2024</t>
+          <t>0483-2025</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D248" t="n">
         <v>1</v>
@@ -6878,23 +6878,23 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0791-2024</t>
+          <t>INFORME 04 ABRIL 2026 0483-2025</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>0795-2024</t>
+          <t>0496-2024</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D249" t="n">
         <v>1</v>
@@ -6904,23 +6904,23 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0795-2024</t>
+          <t>INFORME 04 ABRIL 2026 0496-2024</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0816-2025</t>
+          <t>0496-2026</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D250" t="n">
         <v>1</v>
@@ -6930,23 +6930,23 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0816-2025</t>
+          <t>INFORME 04 ABRIL 2026 0496-2026</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0827-2025</t>
+          <t>0513-2024</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D251" t="n">
         <v>1</v>
@@ -6956,23 +6956,23 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0827-2025</t>
+          <t>INFORME 04 ABRIL 2026 0513-2024</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>0835-2025</t>
+          <t>0525-2023</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D252" t="n">
         <v>1</v>
@@ -6982,23 +6982,23 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0835-2025</t>
+          <t>INFORME 04 ABRIL 2026 0525-2023</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>0837-2024</t>
+          <t>0538-2025</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D253" t="n">
         <v>1</v>
@@ -7008,23 +7008,23 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0837-2024</t>
+          <t>INFORME 04 ABRIL 2026 0538-2025</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>0877-2025</t>
+          <t>0558-2023</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D254" t="n">
         <v>1</v>
@@ -7034,23 +7034,23 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0877-2025</t>
+          <t>INFORME 04 ABRIL 2026 0558-2023</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0890-2025</t>
+          <t>0648-2024</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D255" t="n">
         <v>1</v>
@@ -7060,23 +7060,23 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0890-2025</t>
+          <t>INFORME 04 ABRIL 2026 0648-2024</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>0911-2021</t>
+          <t>0660-2024</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D256" t="n">
         <v>1</v>
@@ -7086,23 +7086,23 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0911-2021</t>
+          <t>INFORME 04 ABRIL 2026 0660-2024</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>0911-2025</t>
+          <t>0715-2025</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D257" t="n">
         <v>1</v>
@@ -7112,23 +7112,23 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0911-2025</t>
+          <t>INFORME 04 ABRIL 2026 0715-2025</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>0935-2024</t>
+          <t>0741-2025</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D258" t="n">
         <v>1</v>
@@ -7138,23 +7138,23 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0935-2024</t>
+          <t>INFORME 04 ABRIL 2026 0741-2025</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>0937-2024</t>
+          <t>0844-2024</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D259" t="n">
         <v>1</v>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0937-2024</t>
+          <t>INFORME 04 ABRIL 2026 0844-2024</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Jose Libardo Zamora</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0948-2021</t>
+          <t>0913-2024</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D260" t="n">
         <v>1</v>
@@ -7190,23 +7190,23 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0948-2021</t>
+          <t>INFORME 04 ABRIL 2026 0913-2024</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Jeison Smith Ortiz Nieto</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>0952-2024</t>
+          <t>0007-2021</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D261" t="n">
         <v>1</v>
@@ -7216,23 +7216,23 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0952-2024</t>
+          <t>INFORME 04 ABRIL 2026 0007-2021</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>0304-2025</t>
+          <t>0015-2023</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D262" t="n">
         <v>1</v>
@@ -7242,23 +7242,23 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0304-2025</t>
+          <t>INFORME 04 ABRIL 2026 0015-2023</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>0325-2023</t>
+          <t>0035-2024</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D263" t="n">
         <v>1</v>
@@ -7268,23 +7268,23 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0325-2023</t>
+          <t>INFORME 04 ABRIL 2026 0035-2024</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>0370-2023</t>
+          <t>0051-2025</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D264" t="n">
         <v>1</v>
@@ -7294,23 +7294,23 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0370-2023</t>
+          <t>INFORME 04 ABRIL 2026 0051-2025</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>0405-2024</t>
+          <t>0051-2023</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D265" t="n">
         <v>1</v>
@@ -7320,23 +7320,23 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0405-2024</t>
+          <t>INFORME 04 ABRIL 2026 0051-2023</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>0458-2025</t>
+          <t>0055-2023</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D266" t="n">
         <v>1</v>
@@ -7346,23 +7346,23 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0458-2025</t>
+          <t>INFORME 04 ABRIL 2026 0055-2023</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>0464-2022</t>
+          <t>0087-2023</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D267" t="n">
         <v>1</v>
@@ -7372,23 +7372,23 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0464-2022</t>
+          <t>INFORME 04 ABRIL 2026 0087-2023</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0483-2025</t>
+          <t>0102-2024</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D268" t="n">
         <v>1</v>
@@ -7398,23 +7398,23 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0483-2025</t>
+          <t>INFORME 04 ABRIL 2026 0102-2024</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>0496-2024</t>
+          <t>0106-2023</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D269" t="n">
         <v>1</v>
@@ -7424,49 +7424,49 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0496-2024</t>
+          <t>INFORME 04 ABRIL 2026 0106-2023</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>0496-2026</t>
+          <t>0112-2023</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E270" t="n">
         <v>2026</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>INFORME 02 MARZO 2026 0496-2026</t>
+          <t>INFORME 04 ABRIL 2026 0112-2023</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0513-2024</t>
+          <t>0116-2026</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D271" t="n">
         <v>1</v>
@@ -7476,23 +7476,23 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0513-2024</t>
+          <t>INFORME 04 ABRIL 2026 0116-2026</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0525-2023</t>
+          <t>0171-2026</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D272" t="n">
         <v>1</v>
@@ -7502,23 +7502,23 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0525-2023</t>
+          <t>INFORME 04 ABRIL 2026 0171-2026</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0538-2025</t>
+          <t>0185-2025</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D273" t="n">
         <v>1</v>
@@ -7528,23 +7528,23 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0538-2025</t>
+          <t>INFORME 04 ABRIL 2026 0185-2025</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0558-2023</t>
+          <t>0233-2025</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D274" t="n">
         <v>1</v>
@@ -7554,23 +7554,23 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0558-2023</t>
+          <t>INFORME 04 ABRIL 2026 0233-2025</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>0648-2024</t>
+          <t>0282-2022</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D275" t="n">
         <v>1</v>
@@ -7580,23 +7580,23 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0648-2024</t>
+          <t>INFORME 04 ABRIL 2026 0282-2022</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0660-2024</t>
+          <t>0301-2025</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D276" t="n">
         <v>1</v>
@@ -7606,23 +7606,23 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0660-2024</t>
+          <t>INFORME 04 ABRIL 2026 0301-2025</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>0715-2025</t>
+          <t>0336-2024</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D277" t="n">
         <v>1</v>
@@ -7632,23 +7632,23 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0715-2025</t>
+          <t>INFORME 04 ABRIL 2026 0336-2024</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>0741-2025</t>
+          <t>0344-2022</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D278" t="n">
         <v>1</v>
@@ -7658,23 +7658,23 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0741-2025</t>
+          <t>INFORME 04 ABRIL 2026 0344-2022</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>0844-2024</t>
+          <t>0350-2019</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D279" t="n">
         <v>1</v>
@@ -7684,23 +7684,23 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0844-2024</t>
+          <t>INFORME 04 ABRIL 2026 0350-2019</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Jose Libardo Zamora</t>
+          <t>Leidy Tatiana Lopez Algarra</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>0913-2024</t>
+          <t>0358-2025</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D280" t="n">
         <v>1</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0913-2024</t>
+          <t>INFORME 04 ABRIL 2026 0358-2025</t>
         </is>
       </c>
     </row>
@@ -7722,11 +7722,11 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>0015-2023</t>
+          <t>0377-2022</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D281" t="n">
         <v>1</v>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0015-2023</t>
+          <t>INFORME 04 ABRIL 2026 0377-2022</t>
         </is>
       </c>
     </row>
@@ -7748,11 +7748,11 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>0055-2023</t>
+          <t>0444-2024</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D282" t="n">
         <v>1</v>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0055-2023</t>
+          <t>INFORME 04 ABRIL 2026 0444-2024</t>
         </is>
       </c>
     </row>
@@ -7774,11 +7774,11 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>0233-2025</t>
+          <t>0446-2024</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D283" t="n">
         <v>1</v>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0233-2025</t>
+          <t>INFORME 04 ABRIL 2026 0446-2024</t>
         </is>
       </c>
     </row>
@@ -7800,11 +7800,11 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>0282-2022</t>
+          <t>0450-2024</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D284" t="n">
         <v>1</v>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0282-2022</t>
+          <t>INFORME 04 ABRIL 2026 0450-2024</t>
         </is>
       </c>
     </row>
@@ -7826,11 +7826,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0301-2025</t>
+          <t>0464-2025</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D285" t="n">
         <v>1</v>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0301-2025</t>
+          <t>INFORME 04 ABRIL 2026 0464-2025</t>
         </is>
       </c>
     </row>
@@ -7852,11 +7852,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0304-2022</t>
+          <t>0503-2023</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D286" t="n">
         <v>1</v>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0304-2022</t>
+          <t>INFORME 04 ABRIL 2026 0503-2023</t>
         </is>
       </c>
     </row>
@@ -7878,11 +7878,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>0331-2023</t>
+          <t>0506-2023</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D287" t="n">
         <v>1</v>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0331-2023</t>
+          <t>INFORME 04 ABRIL 2026 0506-2023</t>
         </is>
       </c>
     </row>
@@ -7904,11 +7904,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>0336-2024</t>
+          <t>0512-2023</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D288" t="n">
         <v>1</v>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0336-2024</t>
+          <t>INFORME 04 ABRIL 2026 0512-2023</t>
         </is>
       </c>
     </row>
@@ -7930,11 +7930,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>0344-2022</t>
+          <t>0526-2025</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D289" t="n">
         <v>1</v>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0344-2022</t>
+          <t>INFORME 04 ABRIL 2026 0526-2025</t>
         </is>
       </c>
     </row>
@@ -7956,11 +7956,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>0350-2019</t>
+          <t>0529-2020</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D290" t="n">
         <v>1</v>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0350-2019</t>
+          <t>INFORME 04 ABRIL 2026 0529-2020</t>
         </is>
       </c>
     </row>
@@ -7982,11 +7982,11 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>0350-2022</t>
+          <t>0541-2025</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D291" t="n">
         <v>1</v>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0350-2022</t>
+          <t>INFORME 04 ABRIL 2026 0541-2025</t>
         </is>
       </c>
     </row>
@@ -8008,11 +8008,11 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0358-2025</t>
+          <t>0548-2023</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D292" t="n">
         <v>1</v>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0358-2025</t>
+          <t>INFORME 04 ABRIL 2026 0548-2023</t>
         </is>
       </c>
     </row>
@@ -8034,11 +8034,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>0372-2022</t>
+          <t>0565-2024</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D293" t="n">
         <v>1</v>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0372-2022</t>
+          <t>INFORME 04 ABRIL 2026 0565-2024</t>
         </is>
       </c>
     </row>
@@ -8060,11 +8060,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>0377-2022</t>
+          <t>0582-2025</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D294" t="n">
         <v>1</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0377-2022</t>
+          <t>INFORME 04 ABRIL 2026 0582-2025</t>
         </is>
       </c>
     </row>
@@ -8086,11 +8086,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>0444-2024</t>
+          <t>0585-2024</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D295" t="n">
         <v>1</v>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0444-2024</t>
+          <t>INFORME 04 ABRIL 2026 0585-2024</t>
         </is>
       </c>
     </row>
@@ -8112,11 +8112,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>0446-2024</t>
+          <t>0615-2025</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D296" t="n">
         <v>1</v>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0446-2024</t>
+          <t>INFORME 04 ABRIL 2026 0615-2025</t>
         </is>
       </c>
     </row>
@@ -8138,11 +8138,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>0450-2024</t>
+          <t>0616-2025</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D297" t="n">
         <v>1</v>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0450-2024</t>
+          <t>INFORME 04 ABRIL 2026 0616-2025</t>
         </is>
       </c>
     </row>
@@ -8164,11 +8164,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>0464-2025</t>
+          <t>0617-2025</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D298" t="n">
         <v>1</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0464-2025</t>
+          <t>INFORME 04 ABRIL 2026 0617-2025</t>
         </is>
       </c>
     </row>
@@ -8190,11 +8190,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>0503-2023</t>
+          <t>0619-2025</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D299" t="n">
         <v>1</v>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0503-2023</t>
+          <t>INFORME 04 ABRIL 2026 0619-2025</t>
         </is>
       </c>
     </row>
@@ -8216,11 +8216,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>0506-2023</t>
+          <t>0626-2025</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D300" t="n">
         <v>1</v>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0506-2023</t>
+          <t>INFORME 04 ABRIL 2026 0626-2025</t>
         </is>
       </c>
     </row>
@@ -8242,11 +8242,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>0512-2023</t>
+          <t>0628-2025</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D301" t="n">
         <v>1</v>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0512-2023</t>
+          <t>INFORME 04 ABRIL 2026 0628-2025</t>
         </is>
       </c>
     </row>
@@ -8268,11 +8268,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>0515-2024</t>
+          <t>0631-2025</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D302" t="n">
         <v>1</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0515-2024</t>
+          <t>INFORME 04 ABRIL 2026 0631-2025</t>
         </is>
       </c>
     </row>
@@ -8294,11 +8294,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>0526-2025</t>
+          <t>0632-2023</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D303" t="n">
         <v>1</v>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0526-2025</t>
+          <t>INFORME 04 ABRIL 2026 0632-2023</t>
         </is>
       </c>
     </row>
@@ -8320,11 +8320,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>0529-2020</t>
+          <t>0637-2025</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D304" t="n">
         <v>1</v>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0529-2020</t>
+          <t>INFORME 04 ABRIL 2026 0637-2025</t>
         </is>
       </c>
     </row>
@@ -8346,11 +8346,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>0541-2025</t>
+          <t>0640-2024</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D305" t="n">
         <v>1</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0541-2025</t>
+          <t>INFORME 04 ABRIL 2026 0640-2024</t>
         </is>
       </c>
     </row>
@@ -8372,11 +8372,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>0548-2023</t>
+          <t>0644-2025</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D306" t="n">
         <v>1</v>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0548-2023</t>
+          <t>INFORME 04 ABRIL 2026 0644-2025</t>
         </is>
       </c>
     </row>
@@ -8398,11 +8398,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>0565-2024</t>
+          <t>0646-2025</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D307" t="n">
         <v>1</v>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0565-2024</t>
+          <t>INFORME 04 ABRIL 2026 0646-2025</t>
         </is>
       </c>
     </row>
@@ -8424,11 +8424,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>0566-2025</t>
+          <t>0649-2023</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D308" t="n">
         <v>1</v>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0566-2025</t>
+          <t>INFORME 04 ABRIL 2026 0649-2023</t>
         </is>
       </c>
     </row>
@@ -8450,11 +8450,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>0582-2025</t>
+          <t>0652-2025</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D309" t="n">
         <v>1</v>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0582-2025</t>
+          <t>INFORME 04 ABRIL 2026 0652-2025</t>
         </is>
       </c>
     </row>
@@ -8476,11 +8476,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>0585-2024</t>
+          <t>0655-2025</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D310" t="n">
         <v>1</v>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0585-2024</t>
+          <t>INFORME 04 ABRIL 2026 0655-2025</t>
         </is>
       </c>
     </row>
@@ -8502,11 +8502,11 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>0615-2025</t>
+          <t>0657-2024</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D311" t="n">
         <v>1</v>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0615-2025</t>
+          <t>INFORME 04 ABRIL 2026 0657-2024</t>
         </is>
       </c>
     </row>
@@ -8528,11 +8528,11 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>0616-2025</t>
+          <t>0657-2025</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D312" t="n">
         <v>1</v>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0616-2025</t>
+          <t>INFORME 04 ABRIL 2026 0657-2025</t>
         </is>
       </c>
     </row>
@@ -8554,11 +8554,11 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>0617-2025</t>
+          <t>0667-2025</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D313" t="n">
         <v>1</v>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0617-2025</t>
+          <t>INFORME 04 ABRIL 2026 0667-2025</t>
         </is>
       </c>
     </row>
@@ -8580,11 +8580,11 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>0618-2025</t>
+          <t>0669-2024</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D314" t="n">
         <v>1</v>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0618-2025</t>
+          <t>INFORME 04 ABRIL 2026 0669-2024</t>
         </is>
       </c>
     </row>
@@ -8606,11 +8606,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>0619-2025</t>
+          <t>0670-2024</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D315" t="n">
         <v>1</v>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0619-2025</t>
+          <t>INFORME 04 ABRIL 2026 0670-2024</t>
         </is>
       </c>
     </row>
@@ -8632,11 +8632,11 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>0626-2025</t>
+          <t>0672-2025</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D316" t="n">
         <v>1</v>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0626-2025</t>
+          <t>INFORME 04 ABRIL 2026 0672-2025</t>
         </is>
       </c>
     </row>
@@ -8658,11 +8658,11 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>0628-2025</t>
+          <t>0673-2023</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D317" t="n">
         <v>1</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0628-2025</t>
+          <t>INFORME 04 ABRIL 2026 0673-2023</t>
         </is>
       </c>
     </row>
@@ -8684,11 +8684,11 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>0631-2025</t>
+          <t>0674-2021</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D318" t="n">
         <v>1</v>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0631-2025</t>
+          <t>INFORME 04 ABRIL 2026 0674-2021</t>
         </is>
       </c>
     </row>
@@ -8710,11 +8710,11 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>0637-2025</t>
+          <t>0674-2024</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D319" t="n">
         <v>1</v>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0637-2025</t>
+          <t>INFORME 04 ABRIL 2026 0674-2024</t>
         </is>
       </c>
     </row>
@@ -8736,11 +8736,11 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>0640-2024</t>
+          <t>0675-2025</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D320" t="n">
         <v>1</v>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0640-2024</t>
+          <t>INFORME 04 ABRIL 2026 0675-2025</t>
         </is>
       </c>
     </row>
@@ -8762,11 +8762,11 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>0644-2025</t>
+          <t>0678-2025</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D321" t="n">
         <v>1</v>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0644-2025</t>
+          <t>INFORME 04 ABRIL 2026 0678-2025</t>
         </is>
       </c>
     </row>
@@ -8788,11 +8788,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>0646-2025</t>
+          <t>0688-2023</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D322" t="n">
         <v>1</v>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0646-2025</t>
+          <t>INFORME 04 ABRIL 2026 0688-2023</t>
         </is>
       </c>
     </row>
@@ -8814,11 +8814,11 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>0652-2025</t>
+          <t>0688-2025</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D323" t="n">
         <v>1</v>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0652-2025</t>
+          <t>INFORME 04 ABRIL 2026 0688-2025</t>
         </is>
       </c>
     </row>
@@ -8840,11 +8840,11 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>0655-2025</t>
+          <t>0696-2025</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D324" t="n">
         <v>1</v>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0655-2025</t>
+          <t>INFORME 04 ABRIL 2026 0696-2025</t>
         </is>
       </c>
     </row>
@@ -8866,11 +8866,11 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>0657-2024</t>
+          <t>0723-2024</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D325" t="n">
         <v>1</v>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0657-2024</t>
+          <t>INFORME 04 ABRIL 2026 0723-2024</t>
         </is>
       </c>
     </row>
@@ -8892,11 +8892,11 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>0657-2025</t>
+          <t>0723-2025</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D326" t="n">
         <v>1</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0657-2025</t>
+          <t>INFORME 04 ABRIL 2026 0723-2025</t>
         </is>
       </c>
     </row>
@@ -8918,11 +8918,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>0660-2025</t>
+          <t>0726-2024</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D327" t="n">
         <v>1</v>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0660-2025</t>
+          <t>INFORME 04 ABRIL 2026 0726-2024</t>
         </is>
       </c>
     </row>
@@ -8944,11 +8944,11 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>0667-2025</t>
+          <t>0726-2025</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D328" t="n">
         <v>1</v>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0667-2025</t>
+          <t>INFORME 04 ABRIL 2026 0726-2025</t>
         </is>
       </c>
     </row>
@@ -8970,11 +8970,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>0669-2024</t>
+          <t>0737-2025</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D329" t="n">
         <v>1</v>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0669-2024</t>
+          <t>INFORME 04 ABRIL 2026 0737-2025</t>
         </is>
       </c>
     </row>
@@ -8996,11 +8996,11 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>0670-2024</t>
+          <t>0751-2025</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D330" t="n">
         <v>1</v>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0670-2024</t>
+          <t>INFORME 04 ABRIL 2026 0751-2025</t>
         </is>
       </c>
     </row>
@@ -9022,11 +9022,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>0672-2025</t>
+          <t>0753-2025</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D331" t="n">
         <v>1</v>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0672-2025</t>
+          <t>INFORME 04 ABRIL 2026 0753-2025</t>
         </is>
       </c>
     </row>
@@ -9048,11 +9048,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>0673-2023</t>
+          <t>0758-2025</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D332" t="n">
         <v>1</v>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0673-2023</t>
+          <t>INFORME 04 ABRIL 2026 0758-2025</t>
         </is>
       </c>
     </row>
@@ -9074,11 +9074,11 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>0674-2021</t>
+          <t>0759-2025</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D333" t="n">
         <v>1</v>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0674-2021</t>
+          <t>INFORME 04 ABRIL 2026 0759-2025</t>
         </is>
       </c>
     </row>
@@ -9100,11 +9100,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>0674-2024</t>
+          <t>0763-2024</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D334" t="n">
         <v>1</v>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0674-2024</t>
+          <t>INFORME 04 ABRIL 2026 0763-2024</t>
         </is>
       </c>
     </row>
@@ -9126,11 +9126,11 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>0675-2025</t>
+          <t>0769-2023</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D335" t="n">
         <v>1</v>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0675-2025</t>
+          <t>INFORME 04 ABRIL 2026 0769-2023</t>
         </is>
       </c>
     </row>
@@ -9152,11 +9152,11 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>0678-2025</t>
+          <t>0770-2024</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D336" t="n">
         <v>1</v>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0678-2025</t>
+          <t>INFORME 04 ABRIL 2026 0770-2024</t>
         </is>
       </c>
     </row>
@@ -9178,11 +9178,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>0688-2025</t>
+          <t>0783-2025</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D337" t="n">
         <v>1</v>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0688-2025</t>
+          <t>INFORME 04 ABRIL 2026 0783-2025</t>
         </is>
       </c>
     </row>
@@ -9204,11 +9204,11 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>0696-2025</t>
+          <t>0791-2024</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D338" t="n">
         <v>1</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0696-2025</t>
+          <t>INFORME 04 ABRIL 2026 0791-2024</t>
         </is>
       </c>
     </row>
@@ -9230,11 +9230,11 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>0700-2024</t>
+          <t>0795-2025</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D339" t="n">
         <v>1</v>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0700-2024</t>
+          <t>INFORME 04 ABRIL 2026 0795-2025</t>
         </is>
       </c>
     </row>
@@ -9256,11 +9256,11 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>0723-2025</t>
+          <t>0796-2024</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D340" t="n">
         <v>1</v>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0723-2025</t>
+          <t>INFORME 04 ABRIL 2026 0796-2024</t>
         </is>
       </c>
     </row>
@@ -9282,11 +9282,11 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>0726-2025</t>
+          <t>0798-2025</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D341" t="n">
         <v>1</v>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0726-2025</t>
+          <t>INFORME 04 ABRIL 2026 0798-2025</t>
         </is>
       </c>
     </row>
@@ -9308,11 +9308,11 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>0737-2025</t>
+          <t>0801-2024</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D342" t="n">
         <v>1</v>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0737-2025</t>
+          <t>INFORME 04 ABRIL 2026 0801-2024</t>
         </is>
       </c>
     </row>
@@ -9334,11 +9334,11 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>0758-2025</t>
+          <t>0802-2025</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D343" t="n">
         <v>1</v>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0758-2025</t>
+          <t>INFORME 04 ABRIL 2026 0802-2025</t>
         </is>
       </c>
     </row>
@@ -9360,11 +9360,11 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>0763-2024</t>
+          <t>0804-2025</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D344" t="n">
         <v>1</v>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0763-2024</t>
+          <t>INFORME 04 ABRIL 2026 0804-2025</t>
         </is>
       </c>
     </row>
@@ -9386,11 +9386,11 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>0769-2023</t>
+          <t>0807-2024</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D345" t="n">
         <v>1</v>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0769-2023</t>
+          <t>INFORME 04 ABRIL 2026 0807-2024</t>
         </is>
       </c>
     </row>
@@ -9412,11 +9412,11 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>0770-2024</t>
+          <t>0809-2024</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D346" t="n">
         <v>1</v>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0770-2024</t>
+          <t>INFORME 04 ABRIL 2026 0809-2024</t>
         </is>
       </c>
     </row>
@@ -9438,11 +9438,11 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>0783-2025</t>
+          <t>0817-2024</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D347" t="n">
         <v>1</v>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0783-2025</t>
+          <t>INFORME 04 ABRIL 2026 0817-2024</t>
         </is>
       </c>
     </row>
@@ -9464,11 +9464,11 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>0795-2025</t>
+          <t>0833-2025</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D348" t="n">
         <v>1</v>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0795-2025</t>
+          <t>INFORME 04 ABRIL 2026 0833-2025</t>
         </is>
       </c>
     </row>
@@ -9490,11 +9490,11 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>0796-2024</t>
+          <t>0834-2024</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D349" t="n">
         <v>1</v>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0796-2024</t>
+          <t>INFORME 04 ABRIL 2026 0834-2024</t>
         </is>
       </c>
     </row>
@@ -9516,11 +9516,11 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>0798-2025</t>
+          <t>0838-2024</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D350" t="n">
         <v>1</v>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0798-2025</t>
+          <t>INFORME 04 ABRIL 2026 0838-2024</t>
         </is>
       </c>
     </row>
@@ -9542,11 +9542,11 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>0801-2024</t>
+          <t>0839-2025</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D351" t="n">
         <v>1</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0801-2024</t>
+          <t>INFORME 04 ABRIL 2026 0839-2025</t>
         </is>
       </c>
     </row>
@@ -9568,11 +9568,11 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>0802-2025</t>
+          <t>0859-2025</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D352" t="n">
         <v>1</v>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0802-2025</t>
+          <t>INFORME 04 ABRIL 2026 0859-2025</t>
         </is>
       </c>
     </row>
@@ -9594,11 +9594,11 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>0804-2025</t>
+          <t>0863-2025</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D353" t="n">
         <v>1</v>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0804-2025</t>
+          <t>INFORME 04 ABRIL 2026 0863-2025</t>
         </is>
       </c>
     </row>
@@ -9620,11 +9620,11 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>0807-2024</t>
+          <t>0871-2024</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D354" t="n">
         <v>1</v>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0807-2024</t>
+          <t>INFORME 04 ABRIL 2026 0871-2024</t>
         </is>
       </c>
     </row>
@@ -9646,11 +9646,11 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>0809-2024</t>
+          <t>0875-2024</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D355" t="n">
         <v>1</v>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0809-2024</t>
+          <t>INFORME 04 ABRIL 2026 0875-2024</t>
         </is>
       </c>
     </row>
@@ -9672,11 +9672,11 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>0817-2024</t>
+          <t>0903-2024</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D356" t="n">
         <v>1</v>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0817-2024</t>
+          <t>INFORME 04 ABRIL 2026 0903-2024</t>
         </is>
       </c>
     </row>
@@ -9698,11 +9698,11 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>0833-2025</t>
+          <t>0918-2025</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D357" t="n">
         <v>1</v>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0833-2025</t>
+          <t>INFORME 04 ABRIL 2026 0918-2025</t>
         </is>
       </c>
     </row>
@@ -9724,11 +9724,11 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>0834-2024</t>
+          <t>0921-2025</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D358" t="n">
         <v>1</v>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0834-2024</t>
+          <t>INFORME 04 ABRIL 2026 0921-2025</t>
         </is>
       </c>
     </row>
@@ -9750,11 +9750,11 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>0838-2024</t>
+          <t>0928-2024</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D359" t="n">
         <v>1</v>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0838-2024</t>
+          <t>INFORME 04 ABRIL 2026 0928-2024</t>
         </is>
       </c>
     </row>
@@ -9776,11 +9776,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>0839-2025</t>
+          <t>0943-2024</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D360" t="n">
         <v>1</v>
@@ -9790,23 +9790,23 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0839-2025</t>
+          <t>INFORME 04 ABRIL 2026 0943-2024</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t>Oscar Enciso Alvarez</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>0859-2025</t>
+          <t>0757-2023</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D361" t="n">
         <v>1</v>
@@ -9816,23 +9816,23 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0859-2025</t>
+          <t>INFORME 04 ABRIL 2026 0757-2023</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t>Oscar Enciso Alvarez</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>0863-2025</t>
+          <t>0849-2024</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D362" t="n">
         <v>1</v>
@@ -9842,23 +9842,23 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0863-2025</t>
+          <t>INFORME 04 ABRIL 2026 0849-2024</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>0871-2024</t>
+          <t>0004-2022</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D363" t="n">
         <v>1</v>
@@ -9868,23 +9868,23 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0871-2024</t>
+          <t>INFORME 04 ABRIL 2026 0004-2022</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>0875-2024</t>
+          <t>0138-2025</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D364" t="n">
         <v>1</v>
@@ -9894,23 +9894,23 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0875-2024</t>
+          <t>INFORME 04 ABRIL 2026 0138-2025</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>0903-2024</t>
+          <t>0231-2024</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D365" t="n">
         <v>1</v>
@@ -9920,23 +9920,23 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0903-2024</t>
+          <t>INFORME 04 ABRIL 2026 0231-2024</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>0918-2025</t>
+          <t>0278-2020</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D366" t="n">
         <v>1</v>
@@ -9946,23 +9946,23 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0918-2025</t>
+          <t>INFORME 04 ABRIL 2026 0278-2020</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>0921-2025</t>
+          <t>0284-2022</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D367" t="n">
         <v>1</v>
@@ -9972,23 +9972,23 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0921-2025</t>
+          <t>INFORME 04 ABRIL 2026 0284-2022</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>0928-2024</t>
+          <t>0300-2022</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D368" t="n">
         <v>1</v>
@@ -9998,23 +9998,23 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0928-2024</t>
+          <t>INFORME 04 ABRIL 2026 0300-2022</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>0943-2024</t>
+          <t>0513-2023</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D369" t="n">
         <v>1</v>
@@ -10024,23 +10024,23 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0943-2024</t>
+          <t>INFORME 04 ABRIL 2026 0513-2023</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Leidy Tatiana Lopez Algarra</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>0984-2021</t>
+          <t>0518-2025</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D370" t="n">
         <v>1</v>
@@ -10050,23 +10050,23 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0984-2021</t>
+          <t>INFORME 04 ABRIL 2026 0518-2025</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Oscar Enciso Alvarez</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>0643-2024</t>
+          <t>0527-2025</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D371" t="n">
         <v>1</v>
@@ -10076,23 +10076,23 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0643-2024</t>
+          <t>INFORME 04 ABRIL 2026 0527-2025</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Oscar Enciso Alvarez</t>
+          <t xml:space="preserve">Yency Lorena Arboleda </t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>0757-2023</t>
+          <t>0567-2023</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D372" t="n">
         <v>1</v>
@@ -10102,33 +10102,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>INFORME 03 MARZO 2026 0757-2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Oscar Enciso Alvarez</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>0849-2024</t>
-        </is>
-      </c>
-      <c r="C373" t="n">
-        <v>3</v>
-      </c>
-      <c r="D373" t="n">
-        <v>1</v>
-      </c>
-      <c r="E373" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>INFORME 03 MARZO 2026 0849-2024</t>
+          <t>INFORME 04 ABRIL 2026 0567-2023</t>
         </is>
       </c>
     </row>
